--- a/quanlydoan/user_import_template.xlsx
+++ b/quanlydoan/user_import_template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\quanlydoan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\quan-ly-do-an\quanlydoan\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>username</t>
   </si>
@@ -79,6 +79,15 @@
   </si>
   <si>
     <t>SV009</t>
+  </si>
+  <si>
+    <t>gv1@gmaill.com</t>
+  </si>
+  <si>
+    <t>giảng viên 1</t>
+  </si>
+  <si>
+    <t>ROLE_TEACHER</t>
   </si>
 </sst>
 </file>
@@ -438,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.28515625" customWidth="1"/>
@@ -540,12 +549,37 @@
         <v>15</v>
       </c>
     </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
+        <v>12345</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4">
+        <v>334123342</v>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1"/>
     <hyperlink ref="D3" r:id="rId2"/>
+    <hyperlink ref="A4" r:id="rId3"/>
+    <hyperlink ref="D4" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>